--- a/human_validation/judge/kor/judge_D023_S002_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D023_S002_P001__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,124 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 야간 근무 끝나고 나면, 배달 음식을 사서 원래 먹으려던 것보다 훨씬 많이 먹어요. 버거 두 개, 감자튀김, 밀크셰이크 같은 거요. 그러고 집에 와서도 차고에서 남은 음식을 또 한 끼처럼 먹어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 그렇게 드신 후에, 만회하려고 하시는 게 있나요? 예를 들면 일부러 토를 하신다든지요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 아니요, 일부러 토하지는 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 폭식장애 (D023) | 배제됨: 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 그런 일 후에 체중이 느는 걸 막으려고 다른 걸 하시나요? 금식이나 과도한 운동, 약물 복용 같은 거요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 아니요, 그 후에 딱히 만회하려고 하는 건 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 폭식장애 (D023) | 배제됨: 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 그렇게 드실 때, 멈출 수 없거나 먹는 양을 통제할 수 없다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네. 일단 시작하면 스위치가 딸깍 켜지는 것 같아요. 속으로 “Roy, 봉지 닫고 들어가”라고 계속 말하는데도, 그냥 계속 손이 가요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 폭식장애 (D023) | 배제됨: 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 평균적으로 이런 일이 일주일에 몇 번 정도 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 지난 몇 달 동안은 보통 적어도 일주일에 한 번은 있었어요. 많은 주는 두세 번 정도고요, 특히 야간 근무를 하거나 라인에서 힘든 하루를 보낸 후에 더 그래요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 폭식장애 (D023) | 배제됨: 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>진단명: 폭식장애 (D023)
 인구통계: 성별 남성 / 나이 54 / 직업상태 production worker / 최종학력 대학 재학
@@ -575,182 +684,38 @@
 증상 지속 기간: 5 months
 추가 요건: The binge eating occurs, on average, at least once a week for 3 months
 주호소 증상 코드: S049
-배경 서술: Roy는 교대 근무 감독직을 고려받는 동시에 CNC 라인의 임시 팀장을 맡아달라는 요청을 받으면서, 하루가 더 길어지고 예측하기 어려워졌으며 서류 업무와 수습생 문제, 안전하게 생산을 이어갈 수 있다는 걸 증명해야 한다는 압박감이 늘어났다. 그 후 5개월에 걸쳐 늦은 근무와 놓친 가족 저녁 식사는, 트럭이나 작업장에서 혼자 배달 음식이나 남은 음식을 많이, 빠르게 먹는 은밀한 습관으로 변해갔고, 그 후에는 배가 너무 불러 아내와 교회 친구들에게 이 패턴을 숨길 만큼 부끄러움을 느꼈다. 그는 여전히 일과 봉사 활동을 계속했지만, 이런 일이 잦아지면서 신중하고 절제력 있다는 그의 자아상이 흔들리기 시작했다. 정기 산업 보건 검진에서 식습관이 얼마나 통제 불능이 되었는지 인정하게 된 후, 그는 결국 공장의 직원 지원 프로그램을 통해 정신건강의학과 진료 의뢰를 받아들였다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 야간 근무 끝나고 나면, 배달 음식을 사서 원래 먹으려던 것보다 훨씬 많이 먹어요. 버거 두 개, 감자튀김, 밀크셰이크 같은 거요. 그러고 집에 와서도 차고에서 남은 음식을 또 한 끼처럼 먹어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 그렇게 드신 후에, 만회하려고 하시는 게 있나요? 예를 들면 일부러 토를 하신다든지요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 아니요, 일부러 토하지는 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 폭식장애 (D023) | 배제됨: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 그런 일 후에 체중이 느는 걸 막으려고 다른 걸 하시나요? 금식이나 과도한 운동, 약물 복용 같은 거요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 아니요, 그 후에 딱히 만회하려고 하는 건 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 폭식장애 (D023) | 배제됨: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 그렇게 드실 때, 멈출 수 없거나 먹는 양을 통제할 수 없다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네. 일단 시작하면 스위치가 딸깍 켜지는 것 같아요. 속으로 “Roy, 봉지 닫고 들어가”라고 계속 말하는데도, 그냥 계속 손이 가요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 폭식장애 (D023) | 배제됨: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 평균적으로 이런 일이 일주일에 몇 번 정도 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 지난 몇 달 동안은 보통 적어도 일주일에 한 번은 있었어요. 많은 주는 두세 번 정도고요, 특히 야간 근무를 하거나 라인에서 힘든 하루를 보낸 후에 더 그래요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
+배경 서술: Roy는 교대 근무 감독직을 고려받는 동시에 CNC 라인의 임시 팀장을 맡아달라는 요청을 받으면서, 하루가 더 길어지고 예측하기 어려워졌으며 서류 업무와 수습생 문제, 안전하게 생산을 이어갈 수 있다는 걸 증명해야 한다는 압박감이 늘어났다. 그 후 5개월에 걸쳐 늦은 근무와 놓친 가족 저녁 식사는, 트럭이나 작업장에서 혼자 배달 음식이나 남은 음식을 많이, 빠르게 먹는 은밀한 습관으로 변해갔고, 그 후에는 배가 너무 불러 아내와 교회 친구들에게 이 패턴을 숨길 만큼 부끄러움을 느꼈다. 그는 여전히 일과 봉사 활동을 계속했지만, 이런 일이 잦아지면서 신중하고 절제력 있다는 그의 자아상이 흔들리기 시작했다. 정기 산업 보건 검진에서 식습관이 얼마나 통제 불능이 되었는지 인정하게 된 후, 그는 결국 공장의 직원 지원 프로그램을 통해 정신건강의학과 진료 의뢰를 받아들였다.
+표집된 증상 목록:
+  - S049 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.
+  - S050 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).
+  - S051 급하게 먹기: 평소보다 훨씬 빠르게 먹음.
+  - S052 불편할 정도로 배부르게 먹기: 불편할 정도로 배가 부를 때까지 먹음.
+  - S054 부끄러움으로 인한 혼자 먹기: 먹는 양이 부끄러워 혼자 먹음.
+  - S055 폭식 후 부정적 정서: 폭식 후 스스로에게 혐오감을 느끼거나 우울해지거나 심한 죄책감을 느낌.</t>
+        </is>
+      </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 폭식장애 (D023) | 배제됨: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 폭식장애 (D023, ICD: F50.81)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: binge_episode (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.; 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).
-  누락: (없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: binge_episode_related (관계=must_include, 요구개수=3, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 급하게 먹기: 평소보다 훨씬 빠르게 먹음.; 불편할 정도로 배부르게 먹기: 불편할 정도로 배가 부를 때까지 먹음.; 배고프지 않은데 먹기: 신체적으로 배고프지 않은데도 많은 양의 음식을 먹음.; 부끄러움으로 인한 혼자 먹기: 먹는 양이 부끄러워 혼자 먹음.; 폭식 후 부정적 정서: 폭식 후 스스로에게 혐오감을 느끼거나 우울해지거나 심한 죄책감을 느낌.</t>
+          <t>의사의 최종 진단: 폭식장애 (D023, ICD: F50.81)
+지속 기간 요건: 없음
+기능적 손상 요건: None
+추가 요건: 없음
+체크리스트 그룹: binge_episode (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.
+  - 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).
+체크리스트 그룹: binge_episode_related (관계=must_include, 요구개수=3, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D023_S002_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D023_S002_P001__gemini-3.8-flash_kor.xlsx
@@ -670,6 +670,11 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -711,11 +716,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D023_S002_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D023_S002_P001__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.1667</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
